--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="Rbeb5732cf0fa4649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="Rfb25d51505b84c28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03302f104fe6457c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b29c2afcfd34aaa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="Rfb25d51505b84c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R17c4b5a2ea7a4df7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b29c2afcfd34aaa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff1c5024fba44bf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R17c4b5a2ea7a4df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R8d508d72d97a42b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff1c5024fba44bf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1b0934e5d5c4fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R8d508d72d97a42b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R8f2ae60a883b4d1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1b0934e5d5c4fe2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0ac6fe1bded429b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/outputs/x-appendtablerows.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R8f2ae60a883b4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="7" r:id="R3e1121b643084885"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0ac6fe1bded429b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc524914ed2e47b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>